--- a/tasks/finalpool/sf-support-agent-performance/groundtruth_workspace/Support_Agent_Performance.xlsx
+++ b/tasks/finalpool/sf-support-agent-performance/groundtruth_workspace/Support_Agent_Performance.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,27 +418,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Agent_Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Skill_Level</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Tickets_Handled</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Avg_Satisfaction</t>
         </is>
@@ -451,7 +447,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,11 +457,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.23</v>
       </c>
     </row>
     <row r="3">
@@ -485,13 +484,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -501,42 +503,48 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>senior</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>senior</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -545,18 +553,21 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -565,13 +576,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -581,51 +595,60 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3510</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>junior</t>
+          <t>senior</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3509</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>senior</t>
+          <t>junior</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3509</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.27</v>
       </c>
     </row>
   </sheetData>
@@ -643,12 +666,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -671,7 +694,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>31588</v>
       </c>
     </row>
     <row r="4">
@@ -682,7 +705,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Ava</t>
         </is>
       </c>
     </row>
@@ -693,7 +716,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
     </row>
   </sheetData>
